--- a/randoms_ER/randoms_ER_annotations_scores.xlsx
+++ b/randoms_ER/randoms_ER_annotations_scores.xlsx
@@ -1,29 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4507"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ku51015\CHMURA\mystuff\Graph-Vizualisation-Rating-Metric-randoms\randoms_ER\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C43A842-0F3B-42E6-98AC-22F4E371E919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="2484" yWindow="204" windowWidth="17760" windowHeight="4044" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="125725"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -59,8 +54,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,7 +88,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -151,7 +146,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -203,7 +198,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -397,24 +392,24 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -440,7 +435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -451,7 +446,7 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>6</v>
@@ -460,13 +455,13 @@
         <v>5</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -492,19 +487,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4">
         <v>7</v>
       </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
       <c r="D4">
         <v>6</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
       <c r="G4">
         <v>2</v>
       </c>
@@ -512,39 +513,186 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
